--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N92_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N92_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.96445800711774</v>
+        <v>6.819224426156633</v>
       </c>
       <c r="D2" t="n">
-        <v>23.61309223714675</v>
+        <v>3.837127488536347</v>
       </c>
       <c r="E2" t="n">
-        <v>3.750280701783172</v>
+        <v>0.6094206140397652</v>
       </c>
       <c r="F2" t="n">
-        <v>6.411350576855041</v>
+        <v>1.041844468738944</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.95368811517994</v>
+        <v>5.354974318716741</v>
       </c>
       <c r="D3" t="n">
-        <v>32.52967624174516</v>
+        <v>5.286072389283588</v>
       </c>
       <c r="E3" t="n">
-        <v>3.750280701783172</v>
+        <v>0.6094206140397652</v>
       </c>
       <c r="F3" t="n">
-        <v>6.411350576855041</v>
+        <v>1.041844468738944</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.00673048631219</v>
+        <v>6.338593704025731</v>
       </c>
       <c r="D4" t="n">
-        <v>39.26715443419953</v>
+        <v>6.380912595557423</v>
       </c>
       <c r="E4" t="n">
-        <v>3.750280701783172</v>
+        <v>0.6094206140397652</v>
       </c>
       <c r="F4" t="n">
-        <v>6.411350576855041</v>
+        <v>1.041844468738944</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
